--- a/artfynd/A 25038-2022 artfynd.xlsx
+++ b/artfynd/A 25038-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25038-2022 artfynd.xlsx
+++ b/artfynd/A 25038-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,210 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122132008</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98140</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Valberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>563638</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7111429</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122131986</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98140</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Valberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563625</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7111439</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25038-2022 artfynd.xlsx
+++ b/artfynd/A 25038-2022 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>122132008</v>
       </c>
       <c r="B3" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>122131986</v>
       </c>
       <c r="B4" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 25038-2022 artfynd.xlsx
+++ b/artfynd/A 25038-2022 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>122131986</v>
       </c>
       <c r="B3" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>122132008</v>
       </c>
       <c r="B4" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 25038-2022 artfynd.xlsx
+++ b/artfynd/A 25038-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131986</v>
+        <v>122132008</v>
       </c>
       <c r="B3" t="n">
         <v>98185</v>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563625</v>
+        <v>563638</v>
       </c>
       <c r="R3" t="n">
-        <v>7111439</v>
+        <v>7111429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132008</v>
+        <v>122131986</v>
       </c>
       <c r="B4" t="n">
         <v>98185</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563638</v>
+        <v>563625</v>
       </c>
       <c r="R4" t="n">
-        <v>7111429</v>
+        <v>7111439</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 25038-2022 artfynd.xlsx
+++ b/artfynd/A 25038-2022 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132008</v>
+        <v>122131986</v>
       </c>
       <c r="B3" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563638</v>
+        <v>563625</v>
       </c>
       <c r="R3" t="n">
-        <v>7111429</v>
+        <v>7111439</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131986</v>
+        <v>122132008</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563625</v>
+        <v>563638</v>
       </c>
       <c r="R4" t="n">
-        <v>7111439</v>
+        <v>7111429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 25038-2022 artfynd.xlsx
+++ b/artfynd/A 25038-2022 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>122131986</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>122132008</v>
       </c>
       <c r="B4" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 25038-2022 artfynd.xlsx
+++ b/artfynd/A 25038-2022 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>122131986</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,11 +821,6 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -909,7 +904,7 @@
         <v>122132008</v>
       </c>
       <c r="B4" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,11 +918,6 @@
       </c>
       <c r="E4" t="n">
         <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 25038-2022 artfynd.xlsx
+++ b/artfynd/A 25038-2022 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131986</v>
+        <v>122132008</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,6 +822,11 @@
       <c r="E3" t="n">
         <v>220787</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -839,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563625</v>
+        <v>563638</v>
       </c>
       <c r="R3" t="n">
-        <v>7111439</v>
+        <v>7111429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132008</v>
+        <v>122131986</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,6 +924,11 @@
       <c r="E4" t="n">
         <v>220787</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -936,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563638</v>
+        <v>563625</v>
       </c>
       <c r="R4" t="n">
-        <v>7111429</v>
+        <v>7111439</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 25038-2022 artfynd.xlsx
+++ b/artfynd/A 25038-2022 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>122132008</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>122131986</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 25038-2022 artfynd.xlsx
+++ b/artfynd/A 25038-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>56494686</v>
       </c>
       <c r="B2" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563385.7782152185</v>
+        <v>563386</v>
       </c>
       <c r="R2" t="n">
-        <v>7111509.261023481</v>
+        <v>7111509</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2015-05-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-05-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132008</v>
+        <v>122131945</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563638</v>
+        <v>563605</v>
       </c>
       <c r="R3" t="n">
-        <v>7111429</v>
+        <v>7111483</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131986</v>
+        <v>122131959</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563625</v>
+        <v>563609</v>
       </c>
       <c r="R4" t="n">
-        <v>7111439</v>
+        <v>7111468</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,6 +980,200 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122131986</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Valberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>563625</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7111439</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122132008</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Valberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>563638</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7111429</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25038-2022 artfynd.xlsx
+++ b/artfynd/A 25038-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56494686</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131945</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131959</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131986</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,8 +1199,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122132008</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>